--- a/Result/analyze_3.xlsx
+++ b/Result/analyze_3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L64"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,57 +436,47 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>
@@ -497,36 +487,30 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3</v>
-      </c>
-      <c r="L2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -537,36 +521,30 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -577,36 +555,30 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
         <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -616,7 +588,9 @@
           <t>AI電力基建</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
@@ -639,12 +613,6 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -655,37 +623,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
         <v>3</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>8</v>
-      </c>
-      <c r="L6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -694,7 +656,9 @@
           <t>光學</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
@@ -711,18 +675,12 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -733,37 +691,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -773,37 +725,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
         <v>8</v>
       </c>
-      <c r="D9" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>5</v>
-      </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I9" t="n">
         <v>3</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>7</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -812,35 +758,31 @@
           <t>其他</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
       <c r="C10" t="n">
         <v>3</v>
       </c>
       <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="n">
+      <c r="H10" t="n">
         <v>4</v>
       </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>4</v>
-      </c>
-      <c r="H10" t="n">
-        <v>3</v>
-      </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
-      </c>
-      <c r="K10" t="n">
-        <v>4</v>
-      </c>
-      <c r="L10" t="n">
         <v>2</v>
       </c>
     </row>
@@ -851,37 +793,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" t="n">
         <v>5</v>
       </c>
-      <c r="D11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" t="n">
-        <v>3</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2</v>
-      </c>
       <c r="I11" t="n">
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -891,36 +827,30 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3</v>
-      </c>
-      <c r="L12" t="n">
         <v>1</v>
       </c>
     </row>
@@ -934,34 +864,28 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3</v>
-      </c>
-      <c r="L13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -971,37 +895,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>6</v>
-      </c>
-      <c r="L14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1011,37 +929,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I15" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -1051,36 +963,30 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>17</v>
-      </c>
-      <c r="L16" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1090,36 +996,32 @@
           <t>封裝測試</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
+      <c r="B17" t="n">
+        <v>7</v>
+      </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="n">
         <v>4</v>
       </c>
-      <c r="E17" t="n">
-        <v>8</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" t="n">
-        <v>4</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
       <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>8</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1128,15 +1030,17 @@
           <t>導線架</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1151,13 +1055,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1170,10 +1068,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -1185,18 +1083,12 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1206,21 +1098,23 @@
           <t>工業自動化</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1229,12 +1123,6 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1244,35 +1132,31 @@
           <t>工業電腦</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>4</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1282,12 +1166,14 @@
           <t>數位雲端</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -1299,18 +1185,12 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1330,13 +1210,13 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1345,13 +1225,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1360,12 +1234,14 @@
           <t>機器人</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -1383,13 +1259,7 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1398,15 +1268,17 @@
           <t>橡膠</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="n">
+        <v>0</v>
+      </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1421,12 +1293,6 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1436,7 +1302,9 @@
           <t>水泥</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="n">
+        <v>0</v>
+      </c>
       <c r="C26" t="n">
         <v>0</v>
       </c>
@@ -1459,12 +1327,6 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1474,12 +1336,14 @@
           <t>汽車</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="n">
+        <v>2</v>
+      </c>
       <c r="C27" t="n">
         <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -1488,7 +1352,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1498,12 +1362,6 @@
       </c>
       <c r="J27" t="n">
         <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>2</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1512,9 +1370,11 @@
           <t>油電燃氣</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="n">
+        <v>0</v>
+      </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -1526,21 +1386,15 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>1</v>
-      </c>
-      <c r="L28" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1551,10 +1405,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -1569,19 +1423,13 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
-      </c>
-      <c r="K29" t="n">
-        <v>2</v>
-      </c>
-      <c r="L29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1590,7 +1438,9 @@
           <t>玻璃</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
@@ -1613,12 +1463,6 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1628,35 +1472,31 @@
           <t>玻璃陶瓷</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
-      </c>
-      <c r="K31" t="n">
-        <v>1</v>
-      </c>
-      <c r="L31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1666,7 +1506,9 @@
           <t>生技</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
@@ -1689,12 +1531,6 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>1</v>
-      </c>
-      <c r="L32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1705,37 +1541,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H33" t="n">
         <v>4</v>
       </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
-      </c>
-      <c r="K33" t="n">
-        <v>7</v>
-      </c>
-      <c r="L33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -1744,12 +1574,14 @@
           <t>石化</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -1764,16 +1596,10 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>1</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -1782,12 +1608,14 @@
           <t>紡織</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
       <c r="C35" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -1799,19 +1627,13 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>2</v>
-      </c>
-      <c r="K35" t="n">
-        <v>4</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -1820,36 +1642,32 @@
           <t>綠能</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="n">
+        <v>2</v>
+      </c>
       <c r="C36" t="n">
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>1</v>
-      </c>
-      <c r="L36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -1858,36 +1676,32 @@
           <t>網通</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
         <v>2</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
-        <v>2</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1896,7 +1710,9 @@
           <t>航空</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
       <c r="C38" t="n">
         <v>0</v>
       </c>
@@ -1919,12 +1735,6 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1941,30 +1751,24 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1975,37 +1779,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
         <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G40" t="n">
         <v>2</v>
       </c>
       <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n">
+        <v>14</v>
+      </c>
+      <c r="J40" t="n">
         <v>4</v>
-      </c>
-      <c r="I40" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="n">
-        <v>2</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2021,10 +1819,10 @@
         <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -2040,12 +1838,6 @@
       </c>
       <c r="J41" t="n">
         <v>0</v>
-      </c>
-      <c r="K41" t="n">
-        <v>1</v>
-      </c>
-      <c r="L41" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2054,12 +1846,14 @@
           <t>記憶體</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
+      <c r="B42" t="n">
+        <v>3</v>
+      </c>
       <c r="C42" t="n">
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -2074,16 +1868,10 @@
         <v>2</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="n">
-        <v>6</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2093,37 +1881,31 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
-      </c>
-      <c r="K43" t="n">
-        <v>1</v>
-      </c>
-      <c r="L43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2133,37 +1915,31 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2172,35 +1948,31 @@
           <t>軍工</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="n">
+        <v>0</v>
+      </c>
       <c r="C45" t="n">
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2210,9 +1982,11 @@
           <t>農業科技</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
+      <c r="B46" t="n">
+        <v>0</v>
+      </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -2233,12 +2007,6 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
-        <v>1</v>
-      </c>
-      <c r="L46" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2252,34 +2020,28 @@
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
         <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
-        <v>2</v>
-      </c>
-      <c r="K47" t="n">
-        <v>2</v>
-      </c>
-      <c r="L47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -2315,12 +2077,6 @@
       <c r="J48" t="n">
         <v>0</v>
       </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
@@ -2329,36 +2085,30 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="n">
         <v>4</v>
       </c>
-      <c r="E49" t="n">
-        <v>5</v>
-      </c>
       <c r="F49" t="n">
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="n">
-        <v>2</v>
-      </c>
-      <c r="L49" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2368,36 +2118,32 @@
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
+      <c r="B50" t="n">
+        <v>0</v>
+      </c>
       <c r="C50" t="n">
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="51">
@@ -2406,7 +2152,9 @@
           <t>醫療通路</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
       <c r="C51" t="n">
         <v>0</v>
       </c>
@@ -2429,12 +2177,6 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2448,10 +2190,10 @@
         <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
@@ -2463,18 +2205,12 @@
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2485,37 +2221,31 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
         <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
@@ -2524,7 +2254,9 @@
           <t>零售</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
+      <c r="B54" t="n">
+        <v>0</v>
+      </c>
       <c r="C54" t="n">
         <v>0</v>
       </c>
@@ -2547,12 +2279,6 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2562,7 +2288,9 @@
           <t>電信</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr"/>
+      <c r="B55" t="n">
+        <v>0</v>
+      </c>
       <c r="C55" t="n">
         <v>0</v>
       </c>
@@ -2585,12 +2313,6 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2600,9 +2322,11 @@
           <t>電動車</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
@@ -2623,12 +2347,6 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2638,21 +2356,23 @@
           <t>電器電纜</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
+      <c r="B57" t="n">
+        <v>0</v>
+      </c>
       <c r="C57" t="n">
         <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2661,12 +2381,6 @@
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2676,12 +2390,14 @@
           <t>電子紙</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
+      <c r="B58" t="n">
+        <v>0</v>
+      </c>
       <c r="C58" t="n">
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -2699,12 +2415,6 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2714,15 +2424,17 @@
           <t>電子通路</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr"/>
+      <c r="B59" t="n">
+        <v>0</v>
+      </c>
       <c r="C59" t="n">
         <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -2731,18 +2443,12 @@
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
         <v>1</v>
       </c>
       <c r="J59" t="n">
-        <v>1</v>
-      </c>
-      <c r="K59" t="n">
-        <v>3</v>
-      </c>
-      <c r="L59" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2753,36 +2459,30 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C60" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D60" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I60" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J60" t="n">
-        <v>1</v>
-      </c>
-      <c r="K60" t="n">
-        <v>4</v>
-      </c>
-      <c r="L60" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2796,34 +2496,28 @@
         <v>0</v>
       </c>
       <c r="C61" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
-        <v>2</v>
-      </c>
-      <c r="K61" t="n">
-        <v>3</v>
-      </c>
-      <c r="L61" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -2832,35 +2526,31 @@
           <t>電腦週邊</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
+      <c r="B62" t="n">
+        <v>5</v>
+      </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E62" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2870,12 +2560,14 @@
           <t>面板</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr"/>
+      <c r="B63" t="n">
+        <v>0</v>
+      </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
@@ -2887,18 +2579,12 @@
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2908,7 +2594,9 @@
           <t>食品</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr"/>
+      <c r="B64" t="n">
+        <v>0</v>
+      </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
@@ -2916,13 +2604,13 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -2932,12 +2620,6 @@
       </c>
       <c r="J64" t="n">
         <v>0</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Result/analyze_3.xlsx
+++ b/Result/analyze_3.xlsx
@@ -975,13 +975,13 @@
         <v>2</v>
       </c>
       <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="n">
         <v>5</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>8</v>
-      </c>
-      <c r="H16" t="n">
-        <v>11</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -1791,7 +1791,7 @@
         <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G40" t="n">
         <v>2</v>
@@ -2088,13 +2088,13 @@
         <v>5</v>
       </c>
       <c r="C49" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D49" t="n">
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>

--- a/Result/analyze_3.xlsx
+++ b/Result/analyze_3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:K64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -477,6 +477,11 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>2</v>
@@ -512,6 +517,9 @@
       </c>
       <c r="J2" t="n">
         <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -521,7 +529,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
@@ -545,6 +553,9 @@
         <v>1</v>
       </c>
       <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -554,11 +565,9 @@
           <t>AI晶片</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>8</v>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
         <v>5</v>
@@ -581,6 +590,9 @@
       <c r="J4" t="n">
         <v>3</v>
       </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -588,9 +600,7 @@
           <t>AI電力基建</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>0</v>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
         <v>0</v>
       </c>
@@ -613,6 +623,9 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -623,7 +636,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
         <v>3</v>
@@ -649,6 +662,9 @@
       <c r="J6" t="n">
         <v>10</v>
       </c>
+      <c r="K6" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -657,7 +673,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -682,6 +698,9 @@
       </c>
       <c r="J7" t="n">
         <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -690,9 +709,7 @@
           <t>光通訊</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>2</v>
-      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
         <v>3</v>
       </c>
@@ -717,6 +734,9 @@
       <c r="J8" t="n">
         <v>6</v>
       </c>
+      <c r="K8" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -725,7 +745,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
         <v>6</v>
@@ -751,6 +771,9 @@
       <c r="J9" t="n">
         <v>3</v>
       </c>
+      <c r="K9" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -759,7 +782,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>3</v>
@@ -774,7 +797,7 @@
         <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
         <v>4</v>
@@ -785,6 +808,9 @@
       <c r="J10" t="n">
         <v>2</v>
       </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -793,7 +819,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
         <v>2</v>
@@ -819,6 +845,9 @@
       <c r="J11" t="n">
         <v>1</v>
       </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -827,7 +856,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
         <v>2</v>
@@ -853,6 +882,9 @@
       <c r="J12" t="n">
         <v>1</v>
       </c>
+      <c r="K12" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -860,9 +892,7 @@
           <t>化學</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
         <v>1</v>
       </c>
@@ -885,6 +915,9 @@
         <v>1</v>
       </c>
       <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
         <v>3</v>
       </c>
     </row>
@@ -895,7 +928,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>4</v>
@@ -921,6 +954,9 @@
       <c r="J14" t="n">
         <v>0</v>
       </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -929,7 +965,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -955,6 +991,9 @@
       <c r="J15" t="n">
         <v>8</v>
       </c>
+      <c r="K15" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -963,7 +1002,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
         <v>6</v>
@@ -989,6 +1028,9 @@
       <c r="J16" t="n">
         <v>3</v>
       </c>
+      <c r="K16" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -997,7 +1039,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>2</v>
@@ -1023,6 +1065,9 @@
       <c r="J17" t="n">
         <v>2</v>
       </c>
+      <c r="K17" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1030,9 +1075,7 @@
           <t>導線架</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
         <v>0</v>
       </c>
@@ -1056,6 +1099,9 @@
       </c>
       <c r="J18" t="n">
         <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1064,9 +1110,7 @@
           <t>居家生活</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
         <v>0</v>
       </c>
@@ -1090,6 +1134,9 @@
       </c>
       <c r="J19" t="n">
         <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1098,9 +1145,7 @@
           <t>工業自動化</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
         <v>2</v>
       </c>
@@ -1124,6 +1169,9 @@
       </c>
       <c r="J20" t="n">
         <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1133,7 +1181,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
         <v>3</v>
@@ -1159,6 +1207,9 @@
       <c r="J21" t="n">
         <v>1</v>
       </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -1167,7 +1218,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
@@ -1191,6 +1242,9 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1227,6 +1281,9 @@
       <c r="J23" t="n">
         <v>1</v>
       </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -1234,9 +1291,7 @@
           <t>機器人</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>1</v>
-      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>0</v>
       </c>
@@ -1260,6 +1315,9 @@
       </c>
       <c r="J24" t="n">
         <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1278,7 +1336,7 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1293,6 +1351,9 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1302,9 +1363,7 @@
           <t>水泥</t>
         </is>
       </c>
-      <c r="B26" t="n">
-        <v>0</v>
-      </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>0</v>
       </c>
@@ -1327,6 +1386,9 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1337,7 +1399,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
         <v>3</v>
@@ -1362,6 +1424,9 @@
       </c>
       <c r="J27" t="n">
         <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1370,9 +1435,7 @@
           <t>油電燃氣</t>
         </is>
       </c>
-      <c r="B28" t="n">
-        <v>0</v>
-      </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>0</v>
       </c>
@@ -1396,6 +1459,9 @@
       </c>
       <c r="J28" t="n">
         <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1405,7 +1471,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
@@ -1429,6 +1495,9 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1438,9 +1507,7 @@
           <t>玻璃</t>
         </is>
       </c>
-      <c r="B30" t="n">
-        <v>0</v>
-      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
         <v>0</v>
       </c>
@@ -1463,6 +1530,9 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1485,18 +1555,21 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1506,9 +1579,7 @@
           <t>生技</t>
         </is>
       </c>
-      <c r="B32" t="n">
-        <v>0</v>
-      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
         <v>0</v>
       </c>
@@ -1531,6 +1602,9 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1541,7 +1615,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
         <v>5</v>
@@ -1567,6 +1641,9 @@
       <c r="J33" t="n">
         <v>3</v>
       </c>
+      <c r="K33" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -1574,9 +1651,7 @@
           <t>石化</t>
         </is>
       </c>
-      <c r="B34" t="n">
-        <v>1</v>
-      </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
         <v>1</v>
       </c>
@@ -1599,6 +1674,9 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1608,9 +1686,7 @@
           <t>紡織</t>
         </is>
       </c>
-      <c r="B35" t="n">
-        <v>0</v>
-      </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
         <v>0</v>
       </c>
@@ -1633,6 +1709,9 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1642,9 +1721,7 @@
           <t>綠能</t>
         </is>
       </c>
-      <c r="B36" t="n">
-        <v>2</v>
-      </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
         <v>1</v>
       </c>
@@ -1667,6 +1744,9 @@
         <v>1</v>
       </c>
       <c r="J36" t="n">
+        <v>2</v>
+      </c>
+      <c r="K36" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1676,9 +1756,7 @@
           <t>網通</t>
         </is>
       </c>
-      <c r="B37" t="n">
-        <v>0</v>
-      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
         <v>5</v>
       </c>
@@ -1703,6 +1781,9 @@
       <c r="J37" t="n">
         <v>1</v>
       </c>
+      <c r="K37" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -1710,9 +1791,7 @@
           <t>航空</t>
         </is>
       </c>
-      <c r="B38" t="n">
-        <v>0</v>
-      </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
         <v>0</v>
       </c>
@@ -1735,6 +1814,9 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1744,9 +1826,7 @@
           <t>航運</t>
         </is>
       </c>
-      <c r="B39" t="n">
-        <v>0</v>
-      </c>
+      <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
         <v>0</v>
       </c>
@@ -1770,6 +1850,9 @@
       </c>
       <c r="J39" t="n">
         <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -1778,9 +1861,7 @@
           <t>被動元件</t>
         </is>
       </c>
-      <c r="B40" t="n">
-        <v>4</v>
-      </c>
+      <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
         <v>0</v>
       </c>
@@ -1805,6 +1886,9 @@
       <c r="J40" t="n">
         <v>4</v>
       </c>
+      <c r="K40" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -1839,6 +1923,9 @@
       <c r="J41" t="n">
         <v>0</v>
       </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
@@ -1846,9 +1933,7 @@
           <t>記憶體</t>
         </is>
       </c>
-      <c r="B42" t="n">
-        <v>3</v>
-      </c>
+      <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
         <v>0</v>
       </c>
@@ -1872,6 +1957,9 @@
       </c>
       <c r="J42" t="n">
         <v>2</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1880,9 +1968,7 @@
           <t>貿易百貨</t>
         </is>
       </c>
-      <c r="B43" t="n">
-        <v>1</v>
-      </c>
+      <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
         <v>0</v>
       </c>
@@ -1905,6 +1991,9 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1915,7 +2004,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -1940,6 +2029,9 @@
       </c>
       <c r="J44" t="n">
         <v>1</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1948,9 +2040,7 @@
           <t>軍工</t>
         </is>
       </c>
-      <c r="B45" t="n">
-        <v>0</v>
-      </c>
+      <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
         <v>0</v>
       </c>
@@ -1973,6 +2063,9 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1982,9 +2075,7 @@
           <t>農業科技</t>
         </is>
       </c>
-      <c r="B46" t="n">
-        <v>0</v>
-      </c>
+      <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
         <v>1</v>
       </c>
@@ -2007,6 +2098,9 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2043,6 +2137,9 @@
       <c r="J47" t="n">
         <v>3</v>
       </c>
+      <c r="K47" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
@@ -2050,9 +2147,7 @@
           <t>造紙</t>
         </is>
       </c>
-      <c r="B48" t="n">
-        <v>0</v>
-      </c>
+      <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
         <v>0</v>
       </c>
@@ -2075,6 +2170,9 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2085,7 +2183,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C49" t="n">
         <v>3</v>
@@ -2111,6 +2209,9 @@
       <c r="J49" t="n">
         <v>0</v>
       </c>
+      <c r="K49" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
@@ -2118,9 +2219,7 @@
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="B50" t="n">
-        <v>0</v>
-      </c>
+      <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
         <v>0</v>
       </c>
@@ -2143,6 +2242,9 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2152,9 +2254,7 @@
           <t>醫療通路</t>
         </is>
       </c>
-      <c r="B51" t="n">
-        <v>0</v>
-      </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
         <v>0</v>
       </c>
@@ -2177,6 +2277,9 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2213,6 +2316,9 @@
       <c r="J52" t="n">
         <v>0</v>
       </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
@@ -2221,13 +2327,13 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C53" t="n">
         <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
@@ -2239,13 +2345,16 @@
         <v>4</v>
       </c>
       <c r="H53" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J53" t="n">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="K53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -2254,9 +2363,7 @@
           <t>零售</t>
         </is>
       </c>
-      <c r="B54" t="n">
-        <v>0</v>
-      </c>
+      <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
         <v>0</v>
       </c>
@@ -2279,6 +2386,9 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2288,9 +2398,7 @@
           <t>電信</t>
         </is>
       </c>
-      <c r="B55" t="n">
-        <v>0</v>
-      </c>
+      <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
         <v>0</v>
       </c>
@@ -2313,6 +2421,9 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2322,9 +2433,7 @@
           <t>電動車</t>
         </is>
       </c>
-      <c r="B56" t="n">
-        <v>1</v>
-      </c>
+      <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
         <v>0</v>
       </c>
@@ -2347,6 +2456,9 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2383,6 +2495,9 @@
       <c r="J57" t="n">
         <v>0</v>
       </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
@@ -2390,9 +2505,7 @@
           <t>電子紙</t>
         </is>
       </c>
-      <c r="B58" t="n">
-        <v>0</v>
-      </c>
+      <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
         <v>0</v>
       </c>
@@ -2415,6 +2528,9 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2424,9 +2540,7 @@
           <t>電子通路</t>
         </is>
       </c>
-      <c r="B59" t="n">
-        <v>0</v>
-      </c>
+      <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
         <v>1</v>
       </c>
@@ -2449,6 +2563,9 @@
         <v>1</v>
       </c>
       <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2459,7 +2576,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C60" t="n">
         <v>3</v>
@@ -2485,6 +2602,9 @@
       <c r="J60" t="n">
         <v>2</v>
       </c>
+      <c r="K60" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
@@ -2519,6 +2639,9 @@
       <c r="J61" t="n">
         <v>0</v>
       </c>
+      <c r="K61" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
@@ -2526,9 +2649,7 @@
           <t>電腦週邊</t>
         </is>
       </c>
-      <c r="B62" t="n">
-        <v>5</v>
-      </c>
+      <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
         <v>3</v>
       </c>
@@ -2551,6 +2672,9 @@
         <v>3</v>
       </c>
       <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2560,9 +2684,7 @@
           <t>面板</t>
         </is>
       </c>
-      <c r="B63" t="n">
-        <v>0</v>
-      </c>
+      <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
         <v>1</v>
       </c>
@@ -2585,6 +2707,9 @@
         <v>0</v>
       </c>
       <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2619,6 +2744,9 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Result/analyze_3.xlsx
+++ b/Result/analyze_3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,52 +436,47 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -492,34 +487,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -532,30 +524,27 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -565,18 +554,20 @@
           <t>AI晶片</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="n">
+        <v>5</v>
+      </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
@@ -585,13 +576,10 @@
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -600,7 +588,9 @@
           <t>AI電力基建</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
@@ -623,9 +613,6 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -636,34 +623,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
         <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>10</v>
-      </c>
-      <c r="K6" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -688,19 +672,16 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -709,9 +690,11 @@
           <t>光通訊</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -720,22 +703,19 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
-        <v>6</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -745,34 +725,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" t="n">
+        <v>12</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" t="n">
         <v>6</v>
       </c>
-      <c r="D9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="J9" t="n">
         <v>8</v>
-      </c>
-      <c r="H9" t="n">
-        <v>12</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3</v>
-      </c>
-      <c r="K9" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -782,34 +759,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
         <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -819,7 +793,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
         <v>2</v>
@@ -828,25 +802,22 @@
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -856,34 +827,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -892,33 +860,32 @@
           <t>化學</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -928,34 +895,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -965,33 +929,30 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>8</v>
-      </c>
-      <c r="K15" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1002,34 +963,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>8</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" t="n">
         <v>6</v>
       </c>
-      <c r="D16" t="n">
-        <v>4</v>
-      </c>
-      <c r="E16" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" t="n">
-        <v>2</v>
-      </c>
-      <c r="G16" t="n">
-        <v>5</v>
-      </c>
-      <c r="H16" t="n">
-        <v>8</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1</v>
-      </c>
       <c r="J16" t="n">
-        <v>3</v>
-      </c>
-      <c r="K16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1039,34 +997,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H17" t="n">
         <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1075,7 +1030,9 @@
           <t>導線架</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
@@ -1092,15 +1049,12 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1110,12 +1064,14 @@
           <t>居家生活</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -1124,18 +1080,15 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1145,32 +1098,31 @@
           <t>工業自動化</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1184,31 +1136,28 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1218,33 +1167,30 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1255,33 +1201,30 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1291,7 +1234,9 @@
           <t>機器人</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
@@ -1308,15 +1253,12 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1330,7 +1272,7 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -1351,9 +1293,6 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1363,7 +1302,9 @@
           <t>水泥</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="n">
+        <v>0</v>
+      </c>
       <c r="C26" t="n">
         <v>0</v>
       </c>
@@ -1386,9 +1327,6 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1399,34 +1337,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -1435,7 +1370,9 @@
           <t>油電燃氣</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="n">
+        <v>0</v>
+      </c>
       <c r="C28" t="n">
         <v>0</v>
       </c>
@@ -1443,24 +1380,21 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
-      </c>
-      <c r="K28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1474,7 +1408,7 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -1483,21 +1417,18 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1507,7 +1438,9 @@
           <t>玻璃</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
@@ -1530,9 +1463,6 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1549,13 +1479,13 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1567,9 +1497,6 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1579,7 +1506,9 @@
           <t>生技</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
@@ -1602,9 +1531,6 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1615,34 +1541,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G33" t="n">
         <v>4</v>
       </c>
       <c r="H33" t="n">
+        <v>3</v>
+      </c>
+      <c r="I33" t="n">
+        <v>3</v>
+      </c>
+      <c r="J33" t="n">
         <v>4</v>
-      </c>
-      <c r="I33" t="n">
-        <v>4</v>
-      </c>
-      <c r="J33" t="n">
-        <v>3</v>
-      </c>
-      <c r="K33" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -1651,12 +1574,14 @@
           <t>石化</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -1668,16 +1593,13 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
-      </c>
-      <c r="K34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1686,7 +1608,9 @@
           <t>紡織</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
       <c r="C35" t="n">
         <v>0</v>
       </c>
@@ -1703,16 +1627,13 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
-      </c>
-      <c r="K35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1721,7 +1642,9 @@
           <t>綠能</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
       <c r="C36" t="n">
         <v>1</v>
       </c>
@@ -1729,24 +1652,21 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
         <v>2</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J36" t="n">
-        <v>2</v>
-      </c>
-      <c r="K36" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1756,9 +1676,11 @@
           <t>網通</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
       <c r="C37" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -1770,18 +1692,15 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
         <v>2</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
-      </c>
-      <c r="K37" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1791,7 +1710,9 @@
           <t>航空</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
       <c r="C38" t="n">
         <v>0</v>
       </c>
@@ -1814,9 +1735,6 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1826,7 +1744,9 @@
           <t>航運</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
       <c r="C39" t="n">
         <v>0</v>
       </c>
@@ -1846,13 +1766,10 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
-      </c>
-      <c r="K39" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -1861,32 +1778,31 @@
           <t>被動元件</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
+      <c r="B40" t="n">
+        <v>0</v>
+      </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I40" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
-        <v>4</v>
-      </c>
-      <c r="K40" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1900,7 +1816,7 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -1921,10 +1837,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -1933,7 +1846,9 @@
           <t>記憶體</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
+      <c r="B42" t="n">
+        <v>0</v>
+      </c>
       <c r="C42" t="n">
         <v>0</v>
       </c>
@@ -1944,21 +1859,18 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H42" t="n">
         <v>2</v>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>2</v>
-      </c>
-      <c r="K42" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1968,7 +1880,9 @@
           <t>貿易百貨</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
+      <c r="B43" t="n">
+        <v>0</v>
+      </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
@@ -1979,21 +1893,18 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2010,28 +1921,25 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>1</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2040,7 +1948,9 @@
           <t>軍工</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="n">
+        <v>0</v>
+      </c>
       <c r="C45" t="n">
         <v>0</v>
       </c>
@@ -2063,9 +1973,6 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2075,9 +1982,11 @@
           <t>農業科技</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
+      <c r="B46" t="n">
+        <v>0</v>
+      </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -2098,9 +2007,6 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2114,31 +2020,28 @@
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
-        <v>3</v>
-      </c>
-      <c r="K47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -2147,7 +2050,9 @@
           <t>造紙</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
+      <c r="B48" t="n">
+        <v>0</v>
+      </c>
       <c r="C48" t="n">
         <v>0</v>
       </c>
@@ -2170,9 +2075,6 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2183,34 +2085,31 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G49" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -2219,15 +2118,17 @@
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -2242,9 +2143,6 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2254,7 +2152,9 @@
           <t>醫療通路</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
       <c r="C51" t="n">
         <v>0</v>
       </c>
@@ -2277,9 +2177,6 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2293,7 +2190,7 @@
         <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
@@ -2302,21 +2199,18 @@
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2327,22 +2221,22 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H53" t="n">
         <v>4</v>
@@ -2351,10 +2245,7 @@
         <v>2</v>
       </c>
       <c r="J53" t="n">
-        <v>3</v>
-      </c>
-      <c r="K53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -2363,7 +2254,9 @@
           <t>零售</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
+      <c r="B54" t="n">
+        <v>0</v>
+      </c>
       <c r="C54" t="n">
         <v>0</v>
       </c>
@@ -2386,9 +2279,6 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2398,7 +2288,9 @@
           <t>電信</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr"/>
+      <c r="B55" t="n">
+        <v>0</v>
+      </c>
       <c r="C55" t="n">
         <v>0</v>
       </c>
@@ -2421,9 +2313,6 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2433,7 +2322,9 @@
           <t>電動車</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
+      <c r="B56" t="n">
+        <v>0</v>
+      </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
@@ -2444,21 +2335,18 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2478,13 +2366,13 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2493,9 +2381,6 @@
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2505,7 +2390,9 @@
           <t>電子紙</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
+      <c r="B58" t="n">
+        <v>0</v>
+      </c>
       <c r="C58" t="n">
         <v>0</v>
       </c>
@@ -2528,9 +2415,6 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2540,32 +2424,31 @@
           <t>電子通路</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr"/>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
       <c r="C59" t="n">
         <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2585,25 +2468,22 @@
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G60" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H60" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I60" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J60" t="n">
-        <v>2</v>
-      </c>
-      <c r="K60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -2613,22 +2493,22 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C61" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2638,9 +2518,6 @@
       </c>
       <c r="J61" t="n">
         <v>0</v>
-      </c>
-      <c r="K61" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -2649,33 +2526,32 @@
           <t>電腦週邊</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
+      <c r="B62" t="n">
+        <v>2</v>
+      </c>
       <c r="C62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -2684,32 +2560,31 @@
           <t>面板</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr"/>
+      <c r="B63" t="n">
+        <v>1</v>
+      </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2723,13 +2598,13 @@
         <v>0</v>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -2744,9 +2619,6 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Result/analyze_3.xlsx
+++ b/Result/analyze_3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:K64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -477,6 +477,11 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -486,9 +491,7 @@
           <t>AI伺服器</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>1</v>
       </c>
@@ -512,6 +515,9 @@
       </c>
       <c r="J2" t="n">
         <v>3</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -520,9 +526,7 @@
           <t>AI應用服務</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>2</v>
       </c>
@@ -545,6 +549,9 @@
         <v>1</v>
       </c>
       <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -554,9 +561,7 @@
           <t>AI晶片</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>5</v>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
         <v>1</v>
       </c>
@@ -580,6 +585,9 @@
       </c>
       <c r="J4" t="n">
         <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -588,9 +596,7 @@
           <t>AI電力基建</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>0</v>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
         <v>0</v>
       </c>
@@ -614,6 +620,9 @@
       </c>
       <c r="J5" t="n">
         <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -622,9 +631,7 @@
           <t>PCB載板</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>8</v>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>1</v>
       </c>
@@ -649,6 +656,9 @@
       <c r="J6" t="n">
         <v>2</v>
       </c>
+      <c r="K6" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -656,9 +666,7 @@
           <t>光學</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
         <v>0</v>
       </c>
@@ -682,6 +690,9 @@
       </c>
       <c r="J7" t="n">
         <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -690,9 +701,7 @@
           <t>光通訊</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
         <v>0</v>
       </c>
@@ -717,6 +726,9 @@
       <c r="J8" t="n">
         <v>0</v>
       </c>
+      <c r="K8" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -724,9 +736,7 @@
           <t>光電</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2</v>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
         <v>2</v>
       </c>
@@ -751,6 +761,9 @@
       <c r="J9" t="n">
         <v>8</v>
       </c>
+      <c r="K9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -759,7 +772,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>2</v>
@@ -768,7 +781,7 @@
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F10" t="n">
         <v>4</v>
@@ -785,6 +798,9 @@
       <c r="J10" t="n">
         <v>2</v>
       </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -793,10 +809,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
         <v>2</v>
@@ -819,6 +835,9 @@
       <c r="J11" t="n">
         <v>3</v>
       </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -826,9 +845,7 @@
           <t>功率元件</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>5</v>
       </c>
@@ -853,6 +870,9 @@
       <c r="J12" t="n">
         <v>1</v>
       </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -860,9 +880,7 @@
           <t>化學</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
         <v>0</v>
       </c>
@@ -887,6 +905,9 @@
       <c r="J13" t="n">
         <v>4</v>
       </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -895,7 +916,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>4</v>
@@ -921,6 +942,9 @@
       <c r="J14" t="n">
         <v>2</v>
       </c>
+      <c r="K14" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -928,9 +952,7 @@
           <t>半導體材料</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>3</v>
-      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>1</v>
       </c>
@@ -955,6 +977,9 @@
       <c r="J15" t="n">
         <v>3</v>
       </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -962,9 +987,7 @@
           <t>半導體設備</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>4</v>
-      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>2</v>
       </c>
@@ -989,6 +1012,9 @@
       <c r="J16" t="n">
         <v>0</v>
       </c>
+      <c r="K16" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -997,7 +1023,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
@@ -1012,16 +1038,19 @@
         <v>2</v>
       </c>
       <c r="G17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1030,9 +1059,7 @@
           <t>導線架</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
         <v>0</v>
       </c>
@@ -1055,6 +1082,9 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1064,9 +1094,7 @@
           <t>居家生活</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
         <v>0</v>
       </c>
@@ -1089,6 +1117,9 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1098,9 +1129,7 @@
           <t>工業自動化</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
         <v>0</v>
       </c>
@@ -1124,6 +1153,9 @@
       </c>
       <c r="J20" t="n">
         <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1132,9 +1164,7 @@
           <t>工業電腦</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>0</v>
       </c>
@@ -1159,6 +1189,9 @@
       <c r="J21" t="n">
         <v>0</v>
       </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -1166,9 +1199,7 @@
           <t>數位雲端</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>1</v>
-      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>0</v>
       </c>
@@ -1191,6 +1222,9 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1201,7 +1235,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -1226,6 +1260,9 @@
       </c>
       <c r="J23" t="n">
         <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1234,9 +1271,7 @@
           <t>機器人</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>0</v>
       </c>
@@ -1259,6 +1294,9 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1268,9 +1306,7 @@
           <t>橡膠</t>
         </is>
       </c>
-      <c r="B25" t="n">
-        <v>0</v>
-      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
         <v>1</v>
       </c>
@@ -1293,6 +1329,9 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1302,9 +1341,7 @@
           <t>水泥</t>
         </is>
       </c>
-      <c r="B26" t="n">
-        <v>0</v>
-      </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>0</v>
       </c>
@@ -1327,6 +1364,9 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1336,9 +1376,7 @@
           <t>汽車</t>
         </is>
       </c>
-      <c r="B27" t="n">
-        <v>1</v>
-      </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>1</v>
       </c>
@@ -1362,6 +1400,9 @@
       </c>
       <c r="J27" t="n">
         <v>2</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1370,9 +1411,7 @@
           <t>油電燃氣</t>
         </is>
       </c>
-      <c r="B28" t="n">
-        <v>0</v>
-      </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>0</v>
       </c>
@@ -1395,6 +1434,9 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1431,6 +1473,9 @@
       <c r="J29" t="n">
         <v>0</v>
       </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -1438,9 +1483,7 @@
           <t>玻璃</t>
         </is>
       </c>
-      <c r="B30" t="n">
-        <v>0</v>
-      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
         <v>0</v>
       </c>
@@ -1464,6 +1507,9 @@
       </c>
       <c r="J30" t="n">
         <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1472,9 +1518,7 @@
           <t>玻璃陶瓷</t>
         </is>
       </c>
-      <c r="B31" t="n">
-        <v>0</v>
-      </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
         <v>0</v>
       </c>
@@ -1497,6 +1541,9 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1506,9 +1553,7 @@
           <t>生技</t>
         </is>
       </c>
-      <c r="B32" t="n">
-        <v>0</v>
-      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
         <v>0</v>
       </c>
@@ -1531,6 +1576,9 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1541,7 +1589,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
         <v>1</v>
@@ -1567,6 +1615,9 @@
       <c r="J33" t="n">
         <v>4</v>
       </c>
+      <c r="K33" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -1574,9 +1625,7 @@
           <t>石化</t>
         </is>
       </c>
-      <c r="B34" t="n">
-        <v>1</v>
-      </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
         <v>0</v>
       </c>
@@ -1600,6 +1649,9 @@
       </c>
       <c r="J34" t="n">
         <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -1608,9 +1660,7 @@
           <t>紡織</t>
         </is>
       </c>
-      <c r="B35" t="n">
-        <v>0</v>
-      </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
         <v>0</v>
       </c>
@@ -1634,6 +1684,9 @@
       </c>
       <c r="J35" t="n">
         <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -1642,9 +1695,7 @@
           <t>綠能</t>
         </is>
       </c>
-      <c r="B36" t="n">
-        <v>0</v>
-      </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
         <v>1</v>
       </c>
@@ -1667,6 +1718,9 @@
         <v>2</v>
       </c>
       <c r="J36" t="n">
+        <v>2</v>
+      </c>
+      <c r="K36" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1676,9 +1730,7 @@
           <t>網通</t>
         </is>
       </c>
-      <c r="B37" t="n">
-        <v>0</v>
-      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
         <v>1</v>
       </c>
@@ -1701,6 +1753,9 @@
         <v>2</v>
       </c>
       <c r="J37" t="n">
+        <v>2</v>
+      </c>
+      <c r="K37" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1710,9 +1765,7 @@
           <t>航空</t>
         </is>
       </c>
-      <c r="B38" t="n">
-        <v>0</v>
-      </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
         <v>0</v>
       </c>
@@ -1735,6 +1788,9 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1744,9 +1800,7 @@
           <t>航運</t>
         </is>
       </c>
-      <c r="B39" t="n">
-        <v>0</v>
-      </c>
+      <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
         <v>0</v>
       </c>
@@ -1769,6 +1823,9 @@
         <v>1</v>
       </c>
       <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1778,9 +1835,7 @@
           <t>被動元件</t>
         </is>
       </c>
-      <c r="B40" t="n">
-        <v>0</v>
-      </c>
+      <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
         <v>1</v>
       </c>
@@ -1805,6 +1860,9 @@
       <c r="J40" t="n">
         <v>1</v>
       </c>
+      <c r="K40" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -1812,9 +1870,7 @@
           <t>觀光</t>
         </is>
       </c>
-      <c r="B41" t="n">
-        <v>0</v>
-      </c>
+      <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
         <v>0</v>
       </c>
@@ -1837,6 +1893,9 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1846,9 +1905,7 @@
           <t>記憶體</t>
         </is>
       </c>
-      <c r="B42" t="n">
-        <v>0</v>
-      </c>
+      <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
         <v>0</v>
       </c>
@@ -1872,6 +1929,9 @@
       </c>
       <c r="J42" t="n">
         <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -1880,9 +1940,7 @@
           <t>貿易百貨</t>
         </is>
       </c>
-      <c r="B43" t="n">
-        <v>0</v>
-      </c>
+      <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
         <v>0</v>
       </c>
@@ -1905,6 +1963,9 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1914,9 +1975,7 @@
           <t>資訊服務</t>
         </is>
       </c>
-      <c r="B44" t="n">
-        <v>0</v>
-      </c>
+      <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
         <v>0</v>
       </c>
@@ -1939,6 +1998,9 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1948,9 +2010,7 @@
           <t>軍工</t>
         </is>
       </c>
-      <c r="B45" t="n">
-        <v>0</v>
-      </c>
+      <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
         <v>0</v>
       </c>
@@ -1973,6 +2033,9 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1982,9 +2045,7 @@
           <t>農業科技</t>
         </is>
       </c>
-      <c r="B46" t="n">
-        <v>0</v>
-      </c>
+      <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
         <v>0</v>
       </c>
@@ -2008,6 +2069,9 @@
       </c>
       <c r="J46" t="n">
         <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -2016,9 +2080,7 @@
           <t>通信網路</t>
         </is>
       </c>
-      <c r="B47" t="n">
-        <v>0</v>
-      </c>
+      <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
         <v>1</v>
       </c>
@@ -2042,6 +2104,9 @@
       </c>
       <c r="J47" t="n">
         <v>1</v>
+      </c>
+      <c r="K47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -2050,9 +2115,7 @@
           <t>造紙</t>
         </is>
       </c>
-      <c r="B48" t="n">
-        <v>0</v>
-      </c>
+      <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
         <v>0</v>
       </c>
@@ -2075,6 +2138,9 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2084,9 +2150,7 @@
           <t>連接器</t>
         </is>
       </c>
-      <c r="B49" t="n">
-        <v>1</v>
-      </c>
+      <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
         <v>1</v>
       </c>
@@ -2111,6 +2175,9 @@
       <c r="J49" t="n">
         <v>2</v>
       </c>
+      <c r="K49" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
@@ -2118,9 +2185,7 @@
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="B50" t="n">
-        <v>1</v>
-      </c>
+      <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
         <v>1</v>
       </c>
@@ -2143,6 +2208,9 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2152,9 +2220,7 @@
           <t>醫療通路</t>
         </is>
       </c>
-      <c r="B51" t="n">
-        <v>0</v>
-      </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
         <v>0</v>
       </c>
@@ -2177,6 +2243,9 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2186,9 +2255,7 @@
           <t>金融</t>
         </is>
       </c>
-      <c r="B52" t="n">
-        <v>0</v>
-      </c>
+      <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
         <v>0</v>
       </c>
@@ -2212,6 +2279,9 @@
       </c>
       <c r="J52" t="n">
         <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -2220,9 +2290,7 @@
           <t>鋼鐵</t>
         </is>
       </c>
-      <c r="B53" t="n">
-        <v>1</v>
-      </c>
+      <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
         <v>0</v>
       </c>
@@ -2247,6 +2315,9 @@
       <c r="J53" t="n">
         <v>0</v>
       </c>
+      <c r="K53" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
@@ -2254,9 +2325,7 @@
           <t>零售</t>
         </is>
       </c>
-      <c r="B54" t="n">
-        <v>0</v>
-      </c>
+      <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
         <v>0</v>
       </c>
@@ -2279,6 +2348,9 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2288,9 +2360,7 @@
           <t>電信</t>
         </is>
       </c>
-      <c r="B55" t="n">
-        <v>0</v>
-      </c>
+      <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
         <v>0</v>
       </c>
@@ -2313,6 +2383,9 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2322,9 +2395,7 @@
           <t>電動車</t>
         </is>
       </c>
-      <c r="B56" t="n">
-        <v>0</v>
-      </c>
+      <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
         <v>0</v>
       </c>
@@ -2347,6 +2418,9 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2356,9 +2430,7 @@
           <t>電器電纜</t>
         </is>
       </c>
-      <c r="B57" t="n">
-        <v>0</v>
-      </c>
+      <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
         <v>0</v>
       </c>
@@ -2381,6 +2453,9 @@
         <v>0</v>
       </c>
       <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2390,9 +2465,7 @@
           <t>電子紙</t>
         </is>
       </c>
-      <c r="B58" t="n">
-        <v>0</v>
-      </c>
+      <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
         <v>0</v>
       </c>
@@ -2415,6 +2488,9 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2424,9 +2500,7 @@
           <t>電子通路</t>
         </is>
       </c>
-      <c r="B59" t="n">
-        <v>1</v>
-      </c>
+      <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
         <v>1</v>
       </c>
@@ -2449,6 +2523,9 @@
         <v>0</v>
       </c>
       <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2458,9 +2535,7 @@
           <t>電子零組件</t>
         </is>
       </c>
-      <c r="B60" t="n">
-        <v>0</v>
-      </c>
+      <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
         <v>3</v>
       </c>
@@ -2485,6 +2560,9 @@
       <c r="J60" t="n">
         <v>1</v>
       </c>
+      <c r="K60" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
@@ -2493,7 +2571,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C61" t="n">
         <v>0</v>
@@ -2519,6 +2597,9 @@
       <c r="J61" t="n">
         <v>0</v>
       </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
@@ -2527,7 +2608,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C62" t="n">
         <v>1</v>
@@ -2551,6 +2632,9 @@
         <v>0</v>
       </c>
       <c r="J62" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2560,9 +2644,7 @@
           <t>面板</t>
         </is>
       </c>
-      <c r="B63" t="n">
-        <v>1</v>
-      </c>
+      <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
         <v>0</v>
       </c>
@@ -2585,6 +2667,9 @@
         <v>0</v>
       </c>
       <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2594,9 +2679,7 @@
           <t>食品</t>
         </is>
       </c>
-      <c r="B64" t="n">
-        <v>0</v>
-      </c>
+      <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
         <v>1</v>
       </c>
@@ -2619,6 +2702,9 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Result/analyze_3.xlsx
+++ b/Result/analyze_3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,52 +436,47 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -491,33 +486,32 @@
           <t>AI伺服器</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -526,18 +520,20 @@
           <t>AI應用服務</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -549,10 +545,7 @@
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -561,12 +554,14 @@
           <t>AI晶片</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -575,19 +570,16 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -596,7 +588,9 @@
           <t>AI電力基建</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
@@ -616,12 +610,9 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -631,33 +622,32 @@
           <t>PCB載板</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>6</v>
+      </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H6" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -666,7 +656,9 @@
           <t>光學</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
@@ -674,24 +666,21 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -701,33 +690,32 @@
           <t>光通訊</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -736,33 +724,32 @@
           <t>光電</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" t="n">
         <v>8</v>
       </c>
-      <c r="F9" t="n">
-        <v>12</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3</v>
-      </c>
-      <c r="H9" t="n">
-        <v>3</v>
-      </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
-        <v>8</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -772,22 +759,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
         <v>2</v>
@@ -797,9 +784,6 @@
       </c>
       <c r="J10" t="n">
         <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -809,34 +793,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -845,32 +826,31 @@
           <t>功率元件</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
         <v>1</v>
       </c>
     </row>
@@ -880,32 +860,31 @@
           <t>化學</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>4</v>
-      </c>
-      <c r="K13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -916,34 +895,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -952,33 +928,32 @@
           <t>半導體材料</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -987,33 +962,32 @@
           <t>半導體設備</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
+      <c r="B16" t="n">
+        <v>2</v>
+      </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1026,31 +1000,28 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F17" t="n">
         <v>2</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1059,7 +1030,9 @@
           <t>導線架</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
@@ -1070,21 +1043,18 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1094,7 +1064,9 @@
           <t>居家生活</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
@@ -1102,24 +1074,21 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1129,32 +1098,31 @@
           <t>工業自動化</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1164,33 +1132,32 @@
           <t>工業電腦</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1199,18 +1166,20 @@
           <t>數位雲端</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1222,9 +1191,6 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1238,30 +1204,27 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1271,7 +1234,9 @@
           <t>機器人</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
@@ -1282,21 +1247,18 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1306,9 +1268,11 @@
           <t>橡膠</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="n">
+        <v>0</v>
+      </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -1329,9 +1293,6 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1341,7 +1302,9 @@
           <t>水泥</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="n">
+        <v>0</v>
+      </c>
       <c r="C26" t="n">
         <v>0</v>
       </c>
@@ -1364,9 +1327,6 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1376,33 +1336,32 @@
           <t>汽車</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>2</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1411,32 +1370,31 @@
           <t>油電燃氣</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="n">
+        <v>0</v>
+      </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1453,13 +1411,13 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1471,10 +1429,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1483,7 +1438,9 @@
           <t>玻璃</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
@@ -1503,13 +1460,10 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1518,7 +1472,9 @@
           <t>玻璃陶瓷</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
       <c r="C31" t="n">
         <v>0</v>
       </c>
@@ -1529,7 +1485,7 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1541,9 +1497,6 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1553,7 +1506,9 @@
           <t>生技</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
@@ -1576,9 +1531,6 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1589,34 +1541,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E33" t="n">
         <v>4</v>
       </c>
       <c r="F33" t="n">
+        <v>3</v>
+      </c>
+      <c r="G33" t="n">
+        <v>3</v>
+      </c>
+      <c r="H33" t="n">
         <v>4</v>
       </c>
-      <c r="G33" t="n">
-        <v>4</v>
-      </c>
-      <c r="H33" t="n">
-        <v>3</v>
-      </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>4</v>
-      </c>
-      <c r="K33" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
@@ -1625,7 +1574,9 @@
           <t>石化</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="n">
+        <v>0</v>
+      </c>
       <c r="C34" t="n">
         <v>0</v>
       </c>
@@ -1636,21 +1587,18 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1660,7 +1608,9 @@
           <t>紡織</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
       <c r="C35" t="n">
         <v>0</v>
       </c>
@@ -1671,22 +1621,19 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -1695,21 +1642,23 @@
           <t>綠能</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
         <v>2</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H36" t="n">
         <v>2</v>
@@ -1718,10 +1667,7 @@
         <v>2</v>
       </c>
       <c r="J36" t="n">
-        <v>2</v>
-      </c>
-      <c r="K36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -1730,7 +1676,9 @@
           <t>網通</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
       <c r="C37" t="n">
         <v>1</v>
       </c>
@@ -1738,24 +1686,21 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" t="n">
         <v>2</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I37" t="n">
         <v>2</v>
       </c>
       <c r="J37" t="n">
-        <v>2</v>
-      </c>
-      <c r="K37" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1765,7 +1710,9 @@
           <t>航空</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
       <c r="C38" t="n">
         <v>0</v>
       </c>
@@ -1788,9 +1735,6 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1800,7 +1744,9 @@
           <t>航運</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
       <c r="C39" t="n">
         <v>0</v>
       </c>
@@ -1814,18 +1760,15 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1835,33 +1778,32 @@
           <t>被動元件</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
+      <c r="B40" t="n">
+        <v>3</v>
+      </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G40" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
-      </c>
-      <c r="K40" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -1870,7 +1812,9 @@
           <t>觀光</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
@@ -1887,16 +1831,13 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
-      </c>
-      <c r="K41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1905,32 +1846,31 @@
           <t>記憶體</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
+      <c r="B42" t="n">
+        <v>0</v>
+      </c>
       <c r="C42" t="n">
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F42" t="n">
         <v>2</v>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1940,18 +1880,20 @@
           <t>貿易百貨</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
+      <c r="B43" t="n">
+        <v>0</v>
+      </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1963,10 +1905,7 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -1975,18 +1914,20 @@
           <t>資訊服務</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
+      <c r="B44" t="n">
+        <v>2</v>
+      </c>
       <c r="C44" t="n">
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1995,13 +1936,10 @@
         <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
-      </c>
-      <c r="K44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2010,7 +1948,9 @@
           <t>軍工</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="n">
+        <v>0</v>
+      </c>
       <c r="C45" t="n">
         <v>0</v>
       </c>
@@ -2033,9 +1973,6 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2045,7 +1982,9 @@
           <t>農業科技</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
+      <c r="B46" t="n">
+        <v>0</v>
+      </c>
       <c r="C46" t="n">
         <v>0</v>
       </c>
@@ -2065,12 +2004,9 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2080,33 +2016,32 @@
           <t>通信網路</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
+      <c r="B47" t="n">
+        <v>0</v>
+      </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I47" t="n">
         <v>2</v>
       </c>
       <c r="J47" t="n">
         <v>1</v>
-      </c>
-      <c r="K47" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -2115,7 +2050,9 @@
           <t>造紙</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
+      <c r="B48" t="n">
+        <v>0</v>
+      </c>
       <c r="C48" t="n">
         <v>0</v>
       </c>
@@ -2138,9 +2075,6 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2150,33 +2084,32 @@
           <t>連接器</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
+      <c r="B49" t="n">
+        <v>0</v>
+      </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I49" t="n">
         <v>3</v>
       </c>
       <c r="J49" t="n">
         <v>2</v>
-      </c>
-      <c r="K49" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -2185,9 +2118,11 @@
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
+      <c r="B50" t="n">
+        <v>0</v>
+      </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -2208,9 +2143,6 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2220,7 +2152,9 @@
           <t>醫療通路</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
       <c r="C51" t="n">
         <v>0</v>
       </c>
@@ -2243,9 +2177,6 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2255,18 +2186,20 @@
           <t>金融</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr"/>
+      <c r="B52" t="n">
+        <v>0</v>
+      </c>
       <c r="C52" t="n">
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -2275,13 +2208,10 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
-      </c>
-      <c r="K52" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -2290,33 +2220,32 @@
           <t>鋼鐵</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E53" t="n">
+        <v>3</v>
+      </c>
+      <c r="F53" t="n">
         <v>4</v>
       </c>
-      <c r="F53" t="n">
-        <v>5</v>
-      </c>
       <c r="G53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H53" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
-      </c>
-      <c r="K53" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -2325,7 +2254,9 @@
           <t>零售</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
+      <c r="B54" t="n">
+        <v>0</v>
+      </c>
       <c r="C54" t="n">
         <v>0</v>
       </c>
@@ -2348,9 +2279,6 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2360,7 +2288,9 @@
           <t>電信</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr"/>
+      <c r="B55" t="n">
+        <v>0</v>
+      </c>
       <c r="C55" t="n">
         <v>0</v>
       </c>
@@ -2383,9 +2313,6 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2395,18 +2322,20 @@
           <t>電動車</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
+      <c r="B56" t="n">
+        <v>0</v>
+      </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -2418,9 +2347,6 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2430,15 +2356,17 @@
           <t>電器電纜</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
+      <c r="B57" t="n">
+        <v>0</v>
+      </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -2453,10 +2381,7 @@
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -2465,7 +2390,9 @@
           <t>電子紙</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
+      <c r="B58" t="n">
+        <v>0</v>
+      </c>
       <c r="C58" t="n">
         <v>0</v>
       </c>
@@ -2488,9 +2415,6 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2500,21 +2424,23 @@
           <t>電子通路</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr"/>
+      <c r="B59" t="n">
+        <v>0</v>
+      </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2523,10 +2449,7 @@
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -2535,33 +2458,32 @@
           <t>電子零組件</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr"/>
+      <c r="B60" t="n">
+        <v>0</v>
+      </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E60" t="n">
+        <v>7</v>
+      </c>
+      <c r="F60" t="n">
+        <v>2</v>
+      </c>
+      <c r="G60" t="n">
+        <v>3</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" t="n">
+        <v>3</v>
+      </c>
+      <c r="J60" t="n">
         <v>4</v>
-      </c>
-      <c r="F60" t="n">
-        <v>4</v>
-      </c>
-      <c r="G60" t="n">
-        <v>7</v>
-      </c>
-      <c r="H60" t="n">
-        <v>2</v>
-      </c>
-      <c r="I60" t="n">
-        <v>3</v>
-      </c>
-      <c r="J60" t="n">
-        <v>1</v>
-      </c>
-      <c r="K60" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -2574,13 +2496,13 @@
         <v>0</v>
       </c>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -2595,10 +2517,7 @@
         <v>1</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -2608,34 +2527,31 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
-        <v>1</v>
-      </c>
-      <c r="K62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -2644,18 +2560,20 @@
           <t>面板</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr"/>
+      <c r="B63" t="n">
+        <v>0</v>
+      </c>
       <c r="C63" t="n">
         <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2667,9 +2585,6 @@
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2679,9 +2594,11 @@
           <t>食品</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr"/>
+      <c r="B64" t="n">
+        <v>0</v>
+      </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
@@ -2702,9 +2619,6 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Result/analyze_3.xlsx
+++ b/Result/analyze_3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:K56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,47 +436,52 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -487,13 +492,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
         <v>3</v>
@@ -502,16 +507,19 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -521,13 +529,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -536,16 +544,19 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -555,19 +566,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -576,9 +587,12 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -589,7 +603,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -607,13 +621,16 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -623,31 +640,34 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>11</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>14</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" t="n">
         <v>6</v>
-      </c>
-      <c r="C6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" t="n">
-        <v>6</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G6" t="n">
-        <v>10</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2</v>
       </c>
       <c r="I6" t="n">
         <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>11</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -660,27 +680,30 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -691,31 +714,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -725,31 +751,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5</v>
+      </c>
+      <c r="J9" t="n">
         <v>6</v>
       </c>
-      <c r="H9" t="n">
-        <v>8</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4</v>
+      <c r="K9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -762,14 +791,14 @@
         <v>2</v>
       </c>
       <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
         <v>5</v>
       </c>
-      <c r="D10" t="n">
-        <v>4</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
       <c r="F10" t="n">
         <v>2</v>
       </c>
@@ -777,13 +806,16 @@
         <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>3</v>
       </c>
       <c r="J10" t="n">
         <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -793,31 +825,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -827,22 +862,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
@@ -851,7 +886,10 @@
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -861,30 +899,33 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -895,13 +936,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -910,15 +951,18 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -929,31 +973,34 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>2</v>
       </c>
       <c r="F15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -966,27 +1013,30 @@
         <v>2</v>
       </c>
       <c r="C16" t="n">
+        <v>8</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" t="n">
         <v>5</v>
       </c>
-      <c r="D16" t="n">
-        <v>8</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="n">
-        <v>3</v>
-      </c>
-      <c r="G16" t="n">
-        <v>6</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>3</v>
-      </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>1</v>
       </c>
     </row>
@@ -997,31 +1047,34 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1034,7 +1087,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -1043,7 +1096,7 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1055,6 +1108,9 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1074,10 +1130,10 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1090,6 +1146,9 @@
       </c>
       <c r="J19" t="n">
         <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1099,10 +1158,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -1114,15 +1173,18 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1133,19 +1195,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
@@ -1157,7 +1219,10 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1173,7 +1238,7 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -1185,13 +1250,16 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1201,7 +1269,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
@@ -1213,7 +1281,7 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1225,6 +1293,9 @@
         <v>1</v>
       </c>
       <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1244,10 +1315,10 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1259,6 +1330,9 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1295,6 +1369,9 @@
       <c r="J25" t="n">
         <v>0</v>
       </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -1329,6 +1406,9 @@
       <c r="J26" t="n">
         <v>0</v>
       </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -1340,7 +1420,7 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -1349,19 +1429,22 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1374,19 +1457,19 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1395,6 +1478,9 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1405,13 +1491,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -1420,7 +1506,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1429,13 +1515,16 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>玻璃</t>
+          <t>玻璃陶瓷</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1448,13 +1537,13 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1463,60 +1552,66 @@
         <v>1</v>
       </c>
       <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷</t>
+          <t>生技醫療</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>生技</t>
+          <t>石化</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -1531,100 +1626,109 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>生技醫療</t>
+          <t>紡織</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>石化</t>
+          <t>綠能</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
         <v>2</v>
       </c>
       <c r="J34" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>紡織</t>
+          <t>網通</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1633,13 +1737,16 @@
         <v>1</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>綠能</t>
+          <t>航空</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1649,78 +1756,84 @@
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>網通</t>
+          <t>航運</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>航空</t>
+          <t>被動元件</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -1732,23 +1845,26 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J38" t="n">
+        <v>8</v>
+      </c>
+      <c r="K38" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>航運</t>
+          <t>觀光</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -1760,7 +1876,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -1769,51 +1885,57 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>被動元件</t>
+          <t>記憶體</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>觀光</t>
+          <t>貿易百貨</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -1831,53 +1953,59 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>記憶體</t>
+          <t>資訊服務</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="K42" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨</t>
+          <t>軍工</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -1887,7 +2015,7 @@
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
@@ -1905,17 +2033,20 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>資訊服務</t>
+          <t>農業科技</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -1927,44 +2058,47 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>軍工</t>
+          <t>通信網路</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1973,13 +2107,16 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
+        <v>4</v>
+      </c>
+      <c r="K45" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>農業科技</t>
+          <t>造紙</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -2004,63 +2141,69 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>通信網路</t>
+          <t>連接器</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H47" t="n">
         <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>造紙</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -2075,47 +2218,53 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>連接器</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>鋼鐵</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -2128,38 +2277,41 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
+        <v>2</v>
+      </c>
+      <c r="K50" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>醫療通路</t>
+          <t>電器電纜</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -2177,23 +2329,26 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>電子通路</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C52" t="n">
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
@@ -2211,115 +2366,127 @@
         <v>1</v>
       </c>
       <c r="J52" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵</t>
+          <t>電子零組件</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C53" t="n">
         <v>4</v>
       </c>
       <c r="D53" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>零售</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="K54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>電信</t>
+          <t>電腦週邊</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="K55" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>電動車</t>
+          <t>食品</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -2329,7 +2496,7 @@
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
@@ -2349,276 +2516,7 @@
       <c r="J56" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t>電器電纜</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>0</v>
-      </c>
-      <c r="C57" t="n">
-        <v>1</v>
-      </c>
-      <c r="D57" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="1" t="inlineStr">
-        <is>
-          <t>電子紙</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>0</v>
-      </c>
-      <c r="C58" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="inlineStr">
-        <is>
-          <t>電子通路</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>0</v>
-      </c>
-      <c r="C59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" t="n">
-        <v>1</v>
-      </c>
-      <c r="F59" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="1" t="inlineStr">
-        <is>
-          <t>電子零組件</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>0</v>
-      </c>
-      <c r="C60" t="n">
-        <v>4</v>
-      </c>
-      <c r="D60" t="n">
-        <v>4</v>
-      </c>
-      <c r="E60" t="n">
-        <v>7</v>
-      </c>
-      <c r="F60" t="n">
-        <v>2</v>
-      </c>
-      <c r="G60" t="n">
-        <v>3</v>
-      </c>
-      <c r="H60" t="n">
-        <v>1</v>
-      </c>
-      <c r="I60" t="n">
-        <v>3</v>
-      </c>
-      <c r="J60" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="1" t="inlineStr">
-        <is>
-          <t>電機機械</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>0</v>
-      </c>
-      <c r="C61" t="n">
-        <v>4</v>
-      </c>
-      <c r="D61" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" t="n">
-        <v>1</v>
-      </c>
-      <c r="F61" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" t="n">
-        <v>1</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="n">
-        <v>1</v>
-      </c>
-      <c r="J61" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="1" t="inlineStr">
-        <is>
-          <t>電腦週邊</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>3</v>
-      </c>
-      <c r="C62" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" t="n">
-        <v>3</v>
-      </c>
-      <c r="F62" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" t="n">
-        <v>1</v>
-      </c>
-      <c r="I62" t="n">
-        <v>1</v>
-      </c>
-      <c r="J62" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="1" t="inlineStr">
-        <is>
-          <t>面板</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>0</v>
-      </c>
-      <c r="C63" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" t="n">
-        <v>2</v>
-      </c>
-      <c r="E63" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="1" t="inlineStr">
-        <is>
-          <t>食品</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>0</v>
-      </c>
-      <c r="C64" t="n">
-        <v>0</v>
-      </c>
-      <c r="D64" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" t="n">
+      <c r="K56" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Result/analyze_3.xlsx
+++ b/Result/analyze_3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K56"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,52 +436,47 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -492,34 +487,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2" t="n">
         <v>3</v>
       </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -529,25 +521,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
         <v>3</v>
@@ -555,9 +547,6 @@
       <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="n">
-        <v>3</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -569,7 +558,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -578,22 +567,19 @@
         <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -603,13 +589,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -621,15 +607,12 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -640,34 +623,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" t="n">
         <v>11</v>
       </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>14</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2</v>
-      </c>
       <c r="G6" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="J6" t="n">
-        <v>11</v>
-      </c>
-      <c r="K6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -680,30 +660,27 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -714,34 +691,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -751,34 +725,31 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
         <v>4</v>
       </c>
-      <c r="C9" t="n">
-        <v>7</v>
-      </c>
       <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>15</v>
+      </c>
+      <c r="J9" t="n">
         <v>4</v>
-      </c>
-      <c r="E9" t="n">
-        <v>9</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2</v>
-      </c>
-      <c r="I9" t="n">
-        <v>5</v>
-      </c>
-      <c r="J9" t="n">
-        <v>6</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -791,31 +762,28 @@
         <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -825,10 +793,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -837,22 +805,19 @@
         <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -862,13 +827,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -877,18 +842,15 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -899,33 +861,30 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
-      </c>
-      <c r="K13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -939,16 +898,16 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -957,13 +916,10 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -973,33 +929,30 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1010,10 +963,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
@@ -1022,22 +975,19 @@
         <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J16" t="n">
-        <v>5</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1047,20 +997,20 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
         <v>3</v>
       </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>3</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
@@ -1068,12 +1018,9 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1087,7 +1034,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -1105,12 +1052,9 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1136,7 +1080,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1146,9 +1090,6 @@
       </c>
       <c r="J19" t="n">
         <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1184,9 +1125,6 @@
       <c r="J20" t="n">
         <v>0</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -1195,13 +1133,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -1210,18 +1148,15 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1238,28 +1173,25 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1269,33 +1201,30 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1315,7 +1244,7 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1324,15 +1253,12 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1369,9 +1295,6 @@
       <c r="J25" t="n">
         <v>0</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -1406,9 +1329,6 @@
       <c r="J26" t="n">
         <v>0</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -1429,7 +1349,7 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
@@ -1441,10 +1361,7 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1457,10 +1374,10 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -1469,7 +1386,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1478,9 +1395,6 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1491,10 +1405,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -1506,19 +1420,16 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1531,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -1543,18 +1454,15 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1565,33 +1473,30 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
         <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
         <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>2</v>
-      </c>
-      <c r="K31" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1602,34 +1507,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
-      </c>
-      <c r="K32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1639,10 +1541,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -1651,21 +1553,18 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1676,33 +1575,30 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
-      </c>
-      <c r="K34" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1713,22 +1609,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1737,10 +1633,7 @@
         <v>1</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
-      </c>
-      <c r="K35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1776,9 +1669,6 @@
       <c r="J36" t="n">
         <v>0</v>
       </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -1790,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -1808,12 +1698,9 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1824,19 +1711,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1848,10 +1735,7 @@
         <v>3</v>
       </c>
       <c r="J38" t="n">
-        <v>8</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -1864,7 +1748,7 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -1879,16 +1763,13 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -1898,33 +1779,30 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
         <v>3</v>
       </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
-      </c>
-      <c r="K40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1935,7 +1813,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -1959,9 +1837,6 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1972,34 +1847,31 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H42" t="n">
         <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>2</v>
-      </c>
-      <c r="K42" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="43">
@@ -2035,9 +1907,6 @@
       <c r="J43" t="n">
         <v>0</v>
       </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -2046,7 +1915,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -2064,15 +1933,12 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2086,30 +1952,27 @@
         <v>1</v>
       </c>
       <c r="C45" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>4</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
         <v>3</v>
       </c>
-      <c r="D45" t="n">
-        <v>2</v>
-      </c>
-      <c r="E45" t="n">
-        <v>2</v>
-      </c>
-      <c r="F45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" t="n">
-        <v>2</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
       <c r="J45" t="n">
-        <v>4</v>
-      </c>
-      <c r="K45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2146,9 +2009,6 @@
       <c r="J46" t="n">
         <v>0</v>
       </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
@@ -2157,34 +2017,31 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E47" t="n">
         <v>3</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>2</v>
+      </c>
+      <c r="I47" t="n">
+        <v>6</v>
+      </c>
+      <c r="J47" t="n">
         <v>3</v>
-      </c>
-      <c r="H47" t="n">
-        <v>1</v>
-      </c>
-      <c r="I47" t="n">
-        <v>3</v>
-      </c>
-      <c r="J47" t="n">
-        <v>5</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -2197,13 +2054,13 @@
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -2212,15 +2069,12 @@
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2234,13 +2088,13 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -2252,12 +2106,9 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2268,22 +2119,22 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50" t="n">
         <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
         <v>1</v>
@@ -2292,9 +2143,6 @@
         <v>1</v>
       </c>
       <c r="J50" t="n">
-        <v>2</v>
-      </c>
-      <c r="K50" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2305,13 +2153,13 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -2326,12 +2174,9 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2342,7 +2187,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C52" t="n">
         <v>0</v>
@@ -2351,10 +2196,10 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -2366,9 +2211,6 @@
         <v>1</v>
       </c>
       <c r="J52" t="n">
-        <v>1</v>
-      </c>
-      <c r="K52" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2379,16 +2221,16 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
         <v>1</v>
@@ -2400,13 +2242,10 @@
         <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J53" t="n">
         <v>1</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -2416,33 +2255,30 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E54" t="n">
         <v>1</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H54" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J54" t="n">
-        <v>4</v>
-      </c>
-      <c r="K54" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2453,34 +2289,31 @@
         </is>
       </c>
       <c r="B55" t="n">
+        <v>2</v>
+      </c>
+      <c r="C55" t="n">
+        <v>2</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="n">
+        <v>2</v>
+      </c>
+      <c r="F55" t="n">
+        <v>2</v>
+      </c>
+      <c r="G55" t="n">
         <v>3</v>
       </c>
-      <c r="C55" t="n">
-        <v>4</v>
-      </c>
-      <c r="D55" t="n">
-        <v>5</v>
-      </c>
-      <c r="E55" t="n">
-        <v>3</v>
-      </c>
-      <c r="F55" t="n">
-        <v>2</v>
-      </c>
-      <c r="G55" t="n">
-        <v>2</v>
-      </c>
       <c r="H55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I55" t="n">
         <v>2</v>
       </c>
       <c r="J55" t="n">
-        <v>2</v>
-      </c>
-      <c r="K55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -2508,15 +2341,12 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Result/analyze_3.xlsx
+++ b/Result/analyze_3.xlsx
@@ -436,47 +436,47 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -487,31 +487,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G2" t="n">
         <v>3</v>
       </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G2" t="n">
-        <v>4</v>
-      </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -521,31 +521,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
         <v>3</v>
       </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
       <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="n">
         <v>3</v>
       </c>
-      <c r="H3" t="n">
-        <v>2</v>
-      </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -555,31 +555,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
         <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -592,10 +592,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
+        <v>11</v>
+      </c>
+      <c r="F6" t="n">
         <v>4</v>
       </c>
-      <c r="F6" t="n">
-        <v>11</v>
-      </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I6" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -657,28 +657,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -691,31 +691,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
         <v>3</v>
       </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -725,31 +725,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>15</v>
+      </c>
+      <c r="I9" t="n">
         <v>4</v>
       </c>
-      <c r="D9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F9" t="n">
-        <v>6</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2</v>
-      </c>
-      <c r="I9" t="n">
-        <v>15</v>
-      </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -759,31 +759,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
         <v>3</v>
       </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -793,28 +793,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -827,16 +827,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -845,10 +845,10 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -861,31 +861,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>2</v>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -901,25 +901,25 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -929,28 +929,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -963,31 +963,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1006,19 +1006,19 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1049,10 +1049,10 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1077,10 +1077,10 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -1148,16 +1148,16 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1170,19 +1170,19 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
@@ -1216,16 +1216,16 @@
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -1337,22 +1337,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1361,7 +1361,7 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -1417,13 +1417,13 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -1439,16 +1439,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -1473,28 +1473,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" t="n">
         <v>2</v>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>2</v>
@@ -1516,7 +1516,7 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
         <v>1</v>
@@ -1528,10 +1528,10 @@
         <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
@@ -1556,10 +1556,10 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -1578,22 +1578,22 @@
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34" t="n">
         <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
         <v>1</v>
@@ -1609,13 +1609,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
         <v>1</v>
@@ -1624,13 +1624,13 @@
         <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -1695,10 +1695,10 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -1717,25 +1717,25 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E38" t="n">
+        <v>8</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
         <v>3</v>
       </c>
-      <c r="F38" t="n">
-        <v>8</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
       <c r="I38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1760,7 +1760,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
         <v>1</v>
@@ -1769,7 +1769,7 @@
         <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1779,28 +1779,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
         <v>3</v>
       </c>
-      <c r="D40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
       <c r="H40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I40" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -1847,28 +1847,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
         <v>2</v>
       </c>
       <c r="F42" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G42" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H42" t="n">
         <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
         <v>2</v>
@@ -1930,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -1949,28 +1949,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2017,31 +2017,31 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="n">
         <v>3</v>
       </c>
-      <c r="D47" t="n">
-        <v>1</v>
-      </c>
       <c r="E47" t="n">
+        <v>5</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>2</v>
+      </c>
+      <c r="H47" t="n">
+        <v>6</v>
+      </c>
+      <c r="I47" t="n">
         <v>3</v>
       </c>
-      <c r="F47" t="n">
-        <v>5</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>2</v>
-      </c>
-      <c r="I47" t="n">
-        <v>6</v>
-      </c>
       <c r="J47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -2066,10 +2066,10 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
@@ -2103,10 +2103,10 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2119,31 +2119,31 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D50" t="n">
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50" t="n">
         <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -2171,10 +2171,10 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -2193,22 +2193,22 @@
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
         <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -2221,31 +2221,31 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -2255,25 +2255,25 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G54" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H54" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I54" t="n">
         <v>2</v>
@@ -2292,25 +2292,25 @@
         <v>2</v>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E55" t="n">
         <v>2</v>
       </c>
       <c r="F55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H55" t="n">
         <v>2</v>
       </c>
       <c r="I55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>1</v>
@@ -2338,16 +2338,16 @@
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
